--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tyler_hyposvu\UW\ECE554\ECE554_Capstone\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0656789-0FC9-411B-ABF7-DDACA83C2979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
   <si>
     <t>Project Part</t>
   </si>
@@ -75,9 +84,6 @@
     <t xml:space="preserve">Tyler Chen </t>
   </si>
   <si>
-    <t>Order Books (Full level book</t>
-  </si>
-  <si>
     <t>Trading Logic (Volatility)</t>
   </si>
   <si>
@@ -151,31 +157,89 @@
   </si>
   <si>
     <t>Poster &amp; Report Work</t>
+  </si>
+  <si>
+    <t>Before Spring Break</t>
+  </si>
+  <si>
+    <t>3/26 - 4/8</t>
+  </si>
+  <si>
+    <t>4/9 - 4/15</t>
+  </si>
+  <si>
+    <t>4/16 - 4/22</t>
+  </si>
+  <si>
+    <t>4/23 - 4/29</t>
+  </si>
+  <si>
+    <t>Order Price Book Finished and Tested (2 stage pipeline).
+Full Level Book Finished
+Cache is 90% finished, waiting for Refill Engine to support the insert part</t>
+  </si>
+  <si>
+    <t>Refilling Engine with Epoch finsihed.
+Full FLB is tested in simulation.
+Designed an integration test for orderbook.
+Orderbook top module tested in both simulation and integration (7 stage pipeline).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -184,7 +248,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -200,48 +264,53 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -431,24 +500,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.25"/>
-    <col customWidth="1" min="2" max="2" width="38.13"/>
-    <col customWidth="1" min="3" max="3" width="17.75"/>
-    <col customWidth="1" min="4" max="4" width="17.25"/>
-    <col customWidth="1" min="5" max="5" width="96.13"/>
+    <col min="1" max="1" width="26.265625" customWidth="1"/>
+    <col min="2" max="2" width="38.1328125" customWidth="1"/>
+    <col min="3" max="3" width="17.73046875" customWidth="1"/>
+    <col min="4" max="4" width="17.265625" customWidth="1"/>
+    <col min="5" max="5" width="96.1328125" customWidth="1"/>
+    <col min="6" max="6" width="31.9296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -462,8 +536,23 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2">
+      <c r="F1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -477,7 +566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>8</v>
@@ -492,7 +581,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -504,7 +593,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>14</v>
@@ -519,7 +608,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>17</v>
@@ -531,7 +620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" ht="102" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>18</v>
@@ -542,201 +631,195 @@
       <c r="D7" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="F7" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="12.75" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>25</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>15</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="2" t="s">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="C16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="s">
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1" t="s">
+      <c r="D22" s="1"/>
+      <c r="E22" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1" t="s">
+    </row>
+    <row r="23" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2"/>
+      <c r="C23" s="5">
+        <v>46124</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24" s="5">
-        <v>46124.0</v>
+        <v>46128</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
       <c r="B25" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C25" s="5">
-        <v>46128.0</v>
+        <v>46128</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
       <c r="B26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C26" s="5">
-        <v>46128.0</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
       <c r="B27" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="5">
-        <v>46133.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" s="5">
-        <v>46140.0</v>
+        <v>46140</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tyler_hyposvu\UW\ECE554\ECE554_Capstone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanielJL\Documents\GitHub\ECE554_Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0656789-0FC9-411B-ABF7-DDACA83C2979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D900A9-4757-469F-9430-2E92AF1FEA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
   <si>
     <t>Project Part</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>Daniel Lei, Will Strong</t>
-  </si>
-  <si>
-    <t>Just need to put everything together and verify successful logic (profits) once complete</t>
   </si>
   <si>
     <t xml:space="preserve">Risk Management </t>
@@ -183,6 +180,30 @@
 Full FLB is tested in simulation.
 Designed an integration test for orderbook.
 Orderbook top module tested in both simulation and integration (7 stage pipeline).</t>
+  </si>
+  <si>
+    <t>Created but not tested</t>
+  </si>
+  <si>
+    <t>Created and tested in simulation</t>
+  </si>
+  <si>
+    <t>Tested and simulated</t>
+  </si>
+  <si>
+    <t>All submodules are put together and has testbench to verify mid-price, reservation based on inventory , spread based on inventory, and time of day behavior . Can be labelled complete since the core functionality works but want to improve coverage so a few additional test cases will be created to target edge cases.</t>
+  </si>
+  <si>
+    <t>Waiting for submodules to be completed</t>
+  </si>
+  <si>
+    <t>Full top level created and connected with submodules. Testbench created and tests core functionaltiy but want to test extra edge cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New volatility module follows EWMA and is finished and tested </t>
+  </si>
+  <si>
+    <t xml:space="preserve">New volatility module was created but not tested </t>
   </si>
 </sst>
 </file>
@@ -275,7 +296,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -290,6 +311,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -511,18 +538,18 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.265625" customWidth="1"/>
-    <col min="2" max="2" width="38.1328125" customWidth="1"/>
-    <col min="3" max="3" width="17.73046875" customWidth="1"/>
-    <col min="4" max="4" width="17.265625" customWidth="1"/>
-    <col min="5" max="5" width="96.1328125" customWidth="1"/>
-    <col min="6" max="6" width="31.9296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.73046875" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" customWidth="1"/>
+    <col min="2" max="2" width="38.109375" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" customWidth="1"/>
+    <col min="5" max="5" width="96.109375" customWidth="1"/>
+    <col min="6" max="6" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -537,22 +564,22 @@
         <v>3</v>
       </c>
       <c r="F1" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -566,7 +593,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>8</v>
@@ -581,7 +608,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -593,7 +620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
         <v>14</v>
@@ -608,7 +635,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
         <v>17</v>
@@ -620,7 +647,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="102" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="105.6" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
         <v>18</v>
@@ -632,13 +659,13 @@
         <v>7</v>
       </c>
       <c r="F7" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="12.75" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
         <v>20</v>
@@ -649,8 +676,14 @@
       <c r="D8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F8" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
         <v>22</v>
@@ -661,8 +694,10 @@
       <c r="D9" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
         <v>23</v>
@@ -673,8 +708,12 @@
       <c r="D10" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F10" s="11"/>
+      <c r="G10" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="66" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
         <v>24</v>
@@ -685,14 +724,20 @@
       <c r="D11" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E11" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>15</v>
@@ -700,11 +745,13 @@
       <c r="D12" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>13</v>
@@ -712,25 +759,33 @@
       <c r="D13" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="1:10" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>15</v>
@@ -739,9 +794,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>19</v>
@@ -750,70 +805,70 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23" s="5">
         <v>46124</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="B24" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="C24" s="5">
         <v>46128</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B25" s="2" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="B25" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="C25" s="5">
         <v>46128</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
-      <c r="B26" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="C26" s="5">
         <v>46133</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="12.75" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" s="5">
         <v>46140</v>

--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wills\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757CC8BF-479D-4F30-A2D4-A3FF3315DDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
   <si>
     <t>Project Part</t>
   </si>
@@ -217,15 +223,24 @@
   <si>
     <t>Poster &amp; Report Work</t>
   </si>
+  <si>
+    <t>Created and tested with a well developed testbench which will be useful during integration</t>
+  </si>
+  <si>
+    <t>Created using a LUT and tested in simulation</t>
+  </si>
+  <si>
+    <t>Created and tested with another well developed testbench which can be used for integration</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,6 +267,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -262,12 +283,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00ff00"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffff00"/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -288,16 +309,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -305,71 +326,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -380,10 +391,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -421,71 +432,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -513,7 +524,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -536,11 +547,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -549,13 +560,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -565,7 +576,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -574,7 +585,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -583,7 +594,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -591,10 +602,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -659,26 +670,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="16" width="26.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="16" width="38.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="17" width="17.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="16" width="17.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="16" width="96.14785714285713" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="18" width="31.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="18" width="29.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="16" width="29.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -708,7 +718,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -721,14 +731,8 @@
       <c r="D2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
         <v>13</v>
@@ -736,19 +740,14 @@
       <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>15</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    </row>
+    <row r="4" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
         <v>17</v>
@@ -759,14 +758,11 @@
       <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="F4" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>19</v>
@@ -780,17 +776,14 @@
       <c r="E5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
         <v>24</v>
@@ -801,16 +794,11 @@
       <c r="D6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="94.5">
+    </row>
+    <row r="7" spans="1:10" ht="88.5" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>26</v>
@@ -821,18 +809,14 @@
       <c r="D7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="31.5">
+    </row>
+    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
         <v>30</v>
@@ -843,18 +827,14 @@
       <c r="D8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    </row>
+    <row r="9" spans="1:10" ht="26" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
         <v>34</v>
@@ -865,14 +845,12 @@
       <c r="D9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="F9" s="12"/>
+      <c r="G9" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
         <v>35</v>
@@ -883,16 +861,12 @@
       <c r="D10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13" t="s">
+      <c r="F10" s="12"/>
+      <c r="G10" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="70.5">
+    </row>
+    <row r="11" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
         <v>37</v>
@@ -900,23 +874,20 @@
       <c r="C11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
         <v>42</v>
@@ -927,16 +898,12 @@
       <c r="D12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="G12" s="12"/>
+    </row>
+    <row r="13" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
         <v>44</v>
@@ -947,14 +914,12 @@
       <c r="D13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="F13" s="12"/>
+      <c r="G13" s="15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
         <v>45</v>
@@ -965,30 +930,14 @@
       <c r="D14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="35.25">
+    </row>
+    <row r="16" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>49</v>
       </c>
@@ -998,22 +947,17 @@
       <c r="C16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="9"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B17" s="6" t="s">
         <v>53</v>
       </c>
@@ -1023,62 +967,12 @@
       <c r="D17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    </row>
+    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>54</v>
       </c>
@@ -1092,13 +986,8 @@
       <c r="E22" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    </row>
+    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
         <v>57</v>
@@ -1106,85 +995,50 @@
       <c r="C23" s="7">
         <v>46124</v>
       </c>
-      <c r="D23" s="9"/>
       <c r="E23" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="9"/>
+    </row>
+    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="7">
         <v>46128</v>
       </c>
-      <c r="D24" s="9"/>
       <c r="E24" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="9"/>
+    </row>
+    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="6" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="7">
         <v>46128</v>
       </c>
-      <c r="D25" s="9"/>
       <c r="E25" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="9"/>
+    </row>
+    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="6" t="s">
         <v>63</v>
       </c>
       <c r="C26" s="7">
         <v>46133</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="9"/>
+    </row>
+    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="6" t="s">
         <v>64</v>
       </c>
       <c r="C27" s="7">
         <v>46140</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wills\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\OneDrive\Documents\Coding\ECE 554\ECE554_Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757CC8BF-479D-4F30-A2D4-A3FF3315DDF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743FF27F-4A41-410F-9F68-D8D6EDEC6C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="71">
   <si>
     <t>Project Part</t>
   </si>
@@ -69,10 +69,6 @@
   </si>
   <si>
     <t>In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Able to send Packets to and from laptop. Having issues connecting HPS and FPGA logic.
-</t>
   </si>
   <si>
     <t>Parser</t>
@@ -231,6 +227,19 @@
   </si>
   <si>
     <t>Created and tested with another well developed testbench which can be used for integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Able to successfully tranlate lobster file with a working testbench. Needs to be merged with Ethernet IN/OT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Having issues connecting HPS and FPGA logic. Ubuntu linux and FPGA potenitally incompatable?
+</t>
+  </si>
+  <si>
+    <t>Created tcp_sender.py. This program sends test TCP formated packets to FPGA</t>
+  </si>
+  <si>
+    <t>Created hps_tcp_reciever.py and verified packet communcation between laptop and FPGA. Also created tcp_packet_reciever.v but unable to program the board succesfully.</t>
   </si>
 </sst>
 </file>
@@ -240,7 +249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,6 +281,12 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -326,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -368,6 +383,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -675,20 +702,20 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7265625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="96.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.7265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -718,7 +745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -731,8 +758,12 @@
       <c r="D2" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F2" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2"/>
+    </row>
+    <row r="3" spans="1:10" ht="105" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
         <v>13</v>
@@ -743,295 +774,301 @@
       <c r="D3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
+      <c r="E3" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="39" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>18</v>
-      </c>
       <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="88.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:10" ht="102.75" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="11" t="s">
+      <c r="G7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="11" t="s">
+      <c r="G8" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="26" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="12"/>
       <c r="G10" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="G11" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>43</v>
-      </c>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="39" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="D14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="12" t="s">
+    </row>
+    <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="29" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="C16" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H16" s="14" t="s">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B17" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="C17" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23" s="7">
         <v>46124</v>
       </c>
       <c r="E23" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="C24" s="7">
         <v>46128</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="C25" s="7">
         <v>46128</v>
       </c>
       <c r="E25" s="6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="C26" s="7">
         <v>46133</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C27" s="7">
         <v>46140</v>

--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\OneDrive\Documents\Coding\ECE 554\ECE554_Capstone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tyler_hyposvu\UW\ECE554\ECE554_Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743FF27F-4A41-410F-9F68-D8D6EDEC6C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A593B17D-AEDE-471F-988F-8D47DD08E3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -184,9 +184,6 @@
     <t/>
   </si>
   <si>
-    <t>Parser -&gt; OrderBooks tested on board</t>
-  </si>
-  <si>
     <t xml:space="preserve">Future Goals &amp; Roadmap: </t>
   </si>
   <si>
@@ -240,6 +237,9 @@
   </si>
   <si>
     <t>Created hps_tcp_reciever.py and verified packet communcation between laptop and FPGA. Also created tcp_packet_reciever.v but unable to program the board succesfully.</t>
+  </si>
+  <si>
+    <t>OrderBooks tested on board</t>
   </si>
 </sst>
 </file>
@@ -702,20 +702,20 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="96.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.73046875" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96.1328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.86328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.73046875" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -745,7 +745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -759,11 +759,11 @@
         <v>12</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2"/>
     </row>
-    <row r="3" spans="1:10" ht="105" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
         <v>13</v>
@@ -775,16 +775,16 @@
         <v>15</v>
       </c>
       <c r="E3" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="G3" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="19" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="39" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:10" ht="39" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
         <v>16</v>
@@ -796,10 +796,10 @@
         <v>12</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>18</v>
@@ -820,7 +820,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
         <v>23</v>
@@ -835,7 +835,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="102.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="102.75" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>25</v>
@@ -853,7 +853,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
         <v>29</v>
@@ -871,7 +871,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
         <v>33</v>
@@ -884,10 +884,10 @@
       </c>
       <c r="F9" s="12"/>
       <c r="G9" s="15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
         <v>34</v>
@@ -903,7 +903,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="57" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
         <v>36</v>
@@ -924,7 +924,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
         <v>41</v>
@@ -940,7 +940,7 @@
       </c>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:10" ht="39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="39" x14ac:dyDescent="0.45">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
         <v>43</v>
@@ -953,10 +953,10 @@
       </c>
       <c r="F13" s="12"/>
       <c r="G13" s="15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
         <v>44</v>
@@ -974,7 +974,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>48</v>
       </c>
@@ -994,9 +994,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B17" s="6" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>26</v>
@@ -1005,70 +1005,70 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C23" s="7">
         <v>46124</v>
       </c>
       <c r="E23" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="6" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="C24" s="7">
         <v>46128</v>
       </c>
       <c r="E24" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="6" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="C25" s="7">
         <v>46128</v>
       </c>
       <c r="E25" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="6" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="C26" s="7">
         <v>46133</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C27" s="7">
         <v>46140</v>

--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tyler_hyposvu\UW\ECE554\ECE554_Capstone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\OneDrive\Documents\Coding\ECE 554\ECE554_Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A593B17D-AEDE-471F-988F-8D47DD08E3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF1B151-DCDD-4266-88E1-AA24687ECBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>Project Part</t>
   </si>
@@ -229,17 +229,20 @@
     <t xml:space="preserve">Able to successfully tranlate lobster file with a working testbench. Needs to be merged with Ethernet IN/OT </t>
   </si>
   <si>
-    <t xml:space="preserve">Having issues connecting HPS and FPGA logic. Ubuntu linux and FPGA potenitally incompatable?
+    <t>Created tcp_sender.py. This program sends test TCP formated packets to FPGA</t>
+  </si>
+  <si>
+    <t>Created hps_tcp_reciever.py and verified packet communcation between laptop and FPGA. Also created tcp_packet_reciever.v but unable to program the board succesfully.</t>
+  </si>
+  <si>
+    <t>OrderBooks tested on board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed issues connecting HPS and FPGA logic.
 </t>
   </si>
   <si>
-    <t>Created tcp_sender.py. This program sends test TCP formated packets to FPGA</t>
-  </si>
-  <si>
-    <t>Created hps_tcp_reciever.py and verified packet communcation between laptop and FPGA. Also created tcp_packet_reciever.v but unable to program the board succesfully.</t>
-  </si>
-  <si>
-    <t>OrderBooks tested on board</t>
+    <t xml:space="preserve">Fixed issues connecting HPS and FPGA logic. Ethernet Input complete. </t>
   </si>
 </sst>
 </file>
@@ -341,7 +344,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -391,10 +394,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -702,20 +702,20 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.73046875" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="96.1328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.86328125" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.73046875" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -745,7 +745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -763,7 +763,7 @@
       </c>
       <c r="G2"/>
     </row>
-    <row r="3" spans="1:10" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
         <v>13</v>
@@ -775,16 +775,19 @@
         <v>15</v>
       </c>
       <c r="E3" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="G3" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="G3" s="19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="39" x14ac:dyDescent="0.45">
+      <c r="H3" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
         <v>16</v>
@@ -799,7 +802,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>18</v>
@@ -820,7 +823,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
         <v>23</v>
@@ -835,7 +838,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="102.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="88.5" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>25</v>
@@ -853,7 +856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
         <v>29</v>
@@ -871,7 +874,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" ht="26" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
         <v>33</v>
@@ -887,7 +890,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
         <v>34</v>
@@ -903,7 +906,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="57" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
         <v>36</v>
@@ -924,7 +927,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
         <v>41</v>
@@ -940,7 +943,7 @@
       </c>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:10" ht="39" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
         <v>43</v>
@@ -956,7 +959,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
         <v>44</v>
@@ -974,7 +977,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>48</v>
       </c>
@@ -994,9 +997,9 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B17" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>26</v>
@@ -1005,11 +1008,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>52</v>
       </c>
@@ -1024,7 +1027,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
         <v>55</v>
@@ -1036,7 +1039,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="6" t="s">
         <v>57</v>
       </c>
@@ -1047,7 +1050,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
@@ -1058,7 +1061,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="6" t="s">
         <v>61</v>
       </c>
@@ -1066,7 +1069,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="6" t="s">
         <v>62</v>
       </c>

--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\OneDrive\Documents\Coding\ECE 554\ECE554_Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF1B151-DCDD-4266-88E1-AA24687ECBB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D7EC35-B079-412E-AED7-6609ADC0F448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -242,7 +242,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Fixed issues connecting HPS and FPGA logic. Ethernet Input complete. </t>
+    <t>Fixed issues connecting HPS and FPGA logic. Ethernet Input complete. Ethernet Output complete. Need to merge with ITCH translator.</t>
   </si>
 </sst>
 </file>
@@ -292,7 +292,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,6 +307,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF33"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -344,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -395,6 +401,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -402,6 +411,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF66FF33"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -771,8 +785,8 @@
       <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>15</v>
+      <c r="D3" s="19" t="s">
+        <v>12</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>70</v>

--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\OneDrive\Documents\Coding\ECE 554\ECE554_Capstone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tyler_hyposvu\UW\ECE554\ECE554_Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D7EC35-B079-412E-AED7-6609ADC0F448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E86BFE-E4CC-4CC0-A5F0-314309F7C912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-2280" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="76">
   <si>
     <t>Project Part</t>
   </si>
@@ -243,6 +243,18 @@
   </si>
   <si>
     <t>Fixed issues connecting HPS and FPGA logic. Ethernet Input complete. Ethernet Output complete. Need to merge with ITCH translator.</t>
+  </si>
+  <si>
+    <t>Parser to Orderbook</t>
+  </si>
+  <si>
+    <t>Had some misunderstanding about bid/ask input and fixed it accordingly</t>
+  </si>
+  <si>
+    <t>3/26 - 4/8: interacting with button</t>
+  </si>
+  <si>
+    <t>4/9 - 4/15: stored the messages inside a memory and parse through parser and output on the 8 segment display</t>
   </si>
 </sst>
 </file>
@@ -350,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -403,6 +415,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -716,20 +734,20 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7265625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="96.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.7265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.73046875" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96.06640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.73046875" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -759,7 +777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -777,7 +795,7 @@
       </c>
       <c r="G2"/>
     </row>
-    <row r="3" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
         <v>13</v>
@@ -801,7 +819,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="39" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
         <v>16</v>
@@ -816,7 +834,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>18</v>
@@ -837,7 +855,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
         <v>23</v>
@@ -852,7 +870,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="88.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="102.75" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>25</v>
@@ -869,8 +887,11 @@
       <c r="G7" s="11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="H7" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
         <v>29</v>
@@ -888,7 +909,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="26" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
         <v>33</v>
@@ -904,7 +925,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
         <v>34</v>
@@ -920,7 +941,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="57" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
         <v>36</v>
@@ -941,7 +962,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
         <v>41</v>
@@ -957,7 +978,7 @@
       </c>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="39" x14ac:dyDescent="0.45">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
         <v>43</v>
@@ -973,7 +994,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
         <v>44</v>
@@ -991,7 +1012,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
         <v>48</v>
       </c>
@@ -1011,7 +1032,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B17" s="6" t="s">
         <v>69</v>
       </c>
@@ -1021,12 +1042,29 @@
       <c r="D17" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B18" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
         <v>52</v>
       </c>
@@ -1041,7 +1079,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
         <v>55</v>
@@ -1053,7 +1091,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="6" t="s">
         <v>57</v>
       </c>
@@ -1064,7 +1102,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
@@ -1075,7 +1113,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="6" t="s">
         <v>61</v>
       </c>
@@ -1083,7 +1121,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="6" t="s">
         <v>62</v>
       </c>

--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tyler_hyposvu\UW\ECE554\ECE554_Capstone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wills\ECE554\ECE554_Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1E86BFE-E4CC-4CC0-A5F0-314309F7C912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157A8342-A696-454B-B6C6-8B04C55F9C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-2280" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
   <si>
     <t>Project Part</t>
   </si>
@@ -255,6 +255,12 @@
   </si>
   <si>
     <t>4/9 - 4/15: stored the messages inside a memory and parse through parser and output on the 8 segment display</t>
+  </si>
+  <si>
+    <t>Market Simulation</t>
+  </si>
+  <si>
+    <t>Simulation of the market and our FPGA trading logic to work out ideal parameters for risk and liquidity</t>
   </si>
 </sst>
 </file>
@@ -328,7 +334,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -358,11 +364,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC6C6C6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC6C6C6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -417,11 +434,17 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -734,20 +757,20 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.73046875" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="96.06640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.73046875" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7265625" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.7265625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -777,7 +800,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -795,7 +818,7 @@
       </c>
       <c r="G2"/>
     </row>
-    <row r="3" spans="1:10" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" ht="87" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
         <v>13</v>
@@ -819,7 +842,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="39" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
         <v>16</v>
@@ -834,7 +857,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>18</v>
@@ -855,7 +878,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
         <v>23</v>
@@ -870,7 +893,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="102.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" ht="88.5" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>25</v>
@@ -891,7 +914,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
         <v>29</v>
@@ -909,7 +932,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" ht="26" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
         <v>33</v>
@@ -925,7 +948,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
         <v>34</v>
@@ -941,7 +964,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="57" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
         <v>36</v>
@@ -962,7 +985,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
         <v>41</v>
@@ -978,7 +1001,7 @@
       </c>
       <c r="G12" s="12"/>
     </row>
-    <row r="13" spans="1:10" ht="39" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
         <v>43</v>
@@ -994,7 +1017,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
         <v>44</v>
@@ -1012,59 +1035,75 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>50</v>
-      </c>
+    <row r="15" spans="1:10" s="9" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="B15" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="H16" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="B17" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B18" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B18" s="20" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B19" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D19" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
     </row>
-    <row r="22" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>52</v>
       </c>
@@ -1079,7 +1118,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
         <v>55</v>
@@ -1091,7 +1130,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="6" t="s">
         <v>57</v>
       </c>
@@ -1102,7 +1141,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="6" t="s">
         <v>59</v>
       </c>
@@ -1113,7 +1152,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="6" t="s">
         <v>61</v>
       </c>
@@ -1121,7 +1160,7 @@
         <v>46133</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="6" t="s">
         <v>62</v>
       </c>

--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wills\ECE554\ECE554_Capstone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanielJL\Documents\GitHub\ECE554_Capstone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{157A8342-A696-454B-B6C6-8B04C55F9C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C15E0A-ACFB-47DE-8E5F-B0AB7C30C45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
   <si>
     <t>Project Part</t>
   </si>
@@ -261,6 +261,18 @@
   </si>
   <si>
     <t>Simulation of the market and our FPGA trading logic to work out ideal parameters for risk and liquidity</t>
+  </si>
+  <si>
+    <t>Added more tests and fully tested</t>
+  </si>
+  <si>
+    <t>Trading Logic (Time)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tested and works in relation to market open duration </t>
+  </si>
+  <si>
+    <t>Full level testbench complete follows, Avallenda Stoikov algorithm</t>
   </si>
 </sst>
 </file>
@@ -379,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -436,9 +448,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -756,21 +765,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.7265625" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="96.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.81640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.7265625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -800,7 +809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -818,7 +827,7 @@
       </c>
       <c r="G2"/>
     </row>
-    <row r="3" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
         <v>13</v>
@@ -842,7 +851,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
         <v>16</v>
@@ -857,7 +866,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
         <v>18</v>
@@ -878,7 +887,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
         <v>23</v>
@@ -893,7 +902,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="88.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="106.2" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
         <v>25</v>
@@ -914,7 +923,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
         <v>29</v>
@@ -931,8 +940,11 @@
       <c r="G8" s="12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="26" x14ac:dyDescent="0.35">
+      <c r="H8" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
         <v>33</v>
@@ -948,10 +960,10 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>30</v>
@@ -960,211 +972,233 @@
         <v>12</v>
       </c>
       <c r="F10" s="12"/>
-      <c r="G10" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="G10" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>39</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="12"/>
       <c r="G11" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>12</v>
+        <v>37</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="12"/>
-    </row>
-    <row r="13" spans="1:10" ht="38.5" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="F13" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="12"/>
+    </row>
+    <row r="14" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="11" t="s">
+      <c r="D15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G15" s="12" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="9" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="B15" s="21" t="s">
+    <row r="16" spans="1:10" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B16" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C16" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="9" t="s">
+      <c r="D16" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="H16" s="14" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H17" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B18" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G18" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B18" s="6" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B19" s="6" t="s">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B20" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C20" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D20" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1" t="s">
+      <c r="D23" s="1"/>
+      <c r="E23" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6" t="s">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C24" s="7">
         <v>46124</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E24" s="6" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="6" t="s">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="C24" s="7">
-        <v>46128</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="C25" s="7">
         <v>46128</v>
       </c>
       <c r="E25" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="7">
+        <v>46128</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="6" t="s">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C27" s="7">
         <v>46133</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="6" t="s">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C28" s="7">
         <v>46140</v>
       </c>
     </row>

--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanielJL\Documents\GitHub\ECE554_Capstone\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7C15E0A-ACFB-47DE-8E5F-B0AB7C30C45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="88">
   <si>
     <t>Project Part</t>
   </si>
@@ -62,13 +56,26 @@
     <t>Complete</t>
   </si>
   <si>
+    <t xml:space="preserve">Able to successfully tranlate lobster file with a working testbench. Needs to be merged with Ethernet IN/OT </t>
+  </si>
+  <si>
     <t>Ethernet IN/OUT</t>
   </si>
   <si>
     <t>Edward Liu</t>
   </si>
   <si>
-    <t>In Progress</t>
+    <t xml:space="preserve">Fixed issues connecting HPS and FPGA logic.
+</t>
+  </si>
+  <si>
+    <t>Created tcp_sender.py. This program sends test TCP formated packets to FPGA</t>
+  </si>
+  <si>
+    <t>Created hps_tcp_reciever.py and verified packet communcation between laptop and FPGA. Also created tcp_packet_reciever.v but unable to program the board succesfully.</t>
+  </si>
+  <si>
+    <t>Fixed issues connecting HPS and FPGA logic. Ethernet Input complete. Ethernet Output complete. Need to merge with ITCH translator.</t>
   </si>
   <si>
     <t>Parser</t>
@@ -77,6 +84,9 @@
     <t>Will Strong</t>
   </si>
   <si>
+    <t>Created and tested with a well developed testbench which will be useful during integration</t>
+  </si>
+  <si>
     <t>Execution Tracker (Python)</t>
   </si>
   <si>
@@ -96,6 +106,9 @@
   </si>
   <si>
     <t>Written &amp; tested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed this to allow 10 stocks, thought we were operating this a separate way, all cleared now and good. </t>
   </si>
   <si>
     <t>Order Books (Order price book)</t>
@@ -115,6 +128,9 @@
 Orderbook top module tested in both simulation and integration (7 stage pipeline).</t>
   </si>
   <si>
+    <t>Had some misunderstanding about bid/ask input and fixed it accordingly</t>
+  </si>
+  <si>
     <t>Trading Logic (Volatility)</t>
   </si>
   <si>
@@ -127,9 +143,24 @@
     <t xml:space="preserve">New volatility module follows EWMA and is finished and tested </t>
   </si>
   <si>
+    <t>Added more tests and fully tested</t>
+  </si>
+  <si>
     <t>Trading Logic (Ln)</t>
   </si>
   <si>
+    <t>Created using a LUT and tested in simulation</t>
+  </si>
+  <si>
+    <t>Trading Logic (Time)</t>
+  </si>
+  <si>
+    <t>Created but not tested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tested and works in relation to market open duration </t>
+  </si>
+  <si>
     <t>Trading Logic (Division)</t>
   </si>
   <si>
@@ -151,27 +182,39 @@
     <t>Full top level created and connected with submodules. Testbench created and tests core functionaltiy but want to test extra edge cases</t>
   </si>
   <si>
+    <t>Full level testbench complete follows, Avallenda Stoikov algorithm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Risk Management </t>
   </si>
   <si>
     <t>Created &amp; Tested</t>
   </si>
   <si>
+    <t xml:space="preserve">SMall changes needed, had to fix the bounds as were too strict for stock information. </t>
+  </si>
+  <si>
     <t>Order Generator</t>
   </si>
   <si>
+    <t>Created and tested with another well developed testbench which can be used for integration</t>
+  </si>
+  <si>
     <t>Inventory Manager</t>
   </si>
   <si>
     <t>Bret Sell, Daniel Lei</t>
   </si>
   <si>
-    <t>Created but not tested</t>
-  </si>
-  <si>
     <t>Tested and simulated</t>
   </si>
   <si>
+    <t>Market Simulation</t>
+  </si>
+  <si>
+    <t>Simulation of the market and our FPGA trading logic to work out ideal parameters for risk and liquidity</t>
+  </si>
+  <si>
     <t xml:space="preserve">Integration so far: </t>
   </si>
   <si>
@@ -181,7 +224,34 @@
     <t>ModelSim testing completed for this part, working on board test</t>
   </si>
   <si>
-    <t/>
+    <t xml:space="preserve">Completed and is okay on the board. </t>
+  </si>
+  <si>
+    <t>OrderBooks tested on board</t>
+  </si>
+  <si>
+    <t>3/26 - 4/8: interacting with button</t>
+  </si>
+  <si>
+    <t>Parser to Orderbook</t>
+  </si>
+  <si>
+    <t>4/9 - 4/15: stored the messages inside a memory and parse through parser and output on the 8 segment display</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top Level ModelSim test bench </t>
+  </si>
+  <si>
+    <t>in progress</t>
+  </si>
+  <si>
+    <t>testbench works but there are changes that need to be made to some components, potentially tl and ob</t>
+  </si>
+  <si>
+    <t>Started working on testbenhc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testbench was finished and rna on entire project. Everything works together as expected, but some issues that need to be worked out and fixed. Mostly stuff that deals submodules and profits and strategy. </t>
   </si>
   <si>
     <t xml:space="preserve">Future Goals &amp; Roadmap: </t>
@@ -215,70 +285,12 @@
   </si>
   <si>
     <t>Poster &amp; Report Work</t>
-  </si>
-  <si>
-    <t>Created and tested with a well developed testbench which will be useful during integration</t>
-  </si>
-  <si>
-    <t>Created using a LUT and tested in simulation</t>
-  </si>
-  <si>
-    <t>Created and tested with another well developed testbench which can be used for integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Able to successfully tranlate lobster file with a working testbench. Needs to be merged with Ethernet IN/OT </t>
-  </si>
-  <si>
-    <t>Created tcp_sender.py. This program sends test TCP formated packets to FPGA</t>
-  </si>
-  <si>
-    <t>Created hps_tcp_reciever.py and verified packet communcation between laptop and FPGA. Also created tcp_packet_reciever.v but unable to program the board succesfully.</t>
-  </si>
-  <si>
-    <t>OrderBooks tested on board</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fixed issues connecting HPS and FPGA logic.
-</t>
-  </si>
-  <si>
-    <t>Fixed issues connecting HPS and FPGA logic. Ethernet Input complete. Ethernet Output complete. Need to merge with ITCH translator.</t>
-  </si>
-  <si>
-    <t>Parser to Orderbook</t>
-  </si>
-  <si>
-    <t>Had some misunderstanding about bid/ask input and fixed it accordingly</t>
-  </si>
-  <si>
-    <t>3/26 - 4/8: interacting with button</t>
-  </si>
-  <si>
-    <t>4/9 - 4/15: stored the messages inside a memory and parse through parser and output on the 8 segment display</t>
-  </si>
-  <si>
-    <t>Market Simulation</t>
-  </si>
-  <si>
-    <t>Simulation of the market and our FPGA trading logic to work out ideal parameters for risk and liquidity</t>
-  </si>
-  <si>
-    <t>Added more tests and fully tested</t>
-  </si>
-  <si>
-    <t>Trading Logic (Time)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tested and works in relation to market open duration </t>
-  </si>
-  <si>
-    <t>Full level testbench complete follows, Avallenda Stoikov algorithm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
@@ -311,15 +323,15 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -331,22 +343,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FF00ff00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF66ff33"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF66FF33"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFffff00"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -363,115 +374,112 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </left>
       <right style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </right>
       <top style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFC6C6C6"/>
+        <color rgb="FFc6c6c6"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFC6C6C6"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFC6C6C6"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="27">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FF66FF33"/>
-    </mruColors>
-  </colors>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -482,10 +490,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -523,71 +531,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -615,7 +623,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -638,11 +646,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -651,13 +659,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -667,7 +675,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -676,7 +684,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -685,7 +693,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -693,10 +701,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -761,25 +769,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="96.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="23" width="26.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="24" width="38.14785714285715" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="25" width="17.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="23" width="17.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="23" width="96.14785714285713" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="26" width="31.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="26" width="29.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="26" width="29.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="23" width="22.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="23" width="13.719285714285713" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -799,7 +808,7 @@
       <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -809,7 +818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="44.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -822,388 +831,546 @@
       <c r="D2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G2"/>
-    </row>
-    <row r="3" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="E2" s="9"/>
+      <c r="F2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="83.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="39">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E4" s="9"/>
+      <c r="F4" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="31.5">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="11"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="106.2" x14ac:dyDescent="0.3">
+      <c r="E6" s="9"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="94.5">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E7" s="9"/>
+      <c r="F7" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="47.25">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+      <c r="E8" s="9"/>
+      <c r="F8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="27.75">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E9" s="9"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="31.5">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E10" s="9"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="E11" s="9"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="75">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="12"/>
-    </row>
-    <row r="14" spans="1:10" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="E13" s="9"/>
+      <c r="F13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="39">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E14" s="9"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="6"/>
       <c r="B15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="9"/>
+      <c r="F15" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="9" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
+      <c r="G15" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="57.75" customFormat="1" s="16">
+      <c r="A16" s="11"/>
+      <c r="B16" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="9"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="31.5">
+      <c r="A18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="9"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+      <c r="A19" s="9"/>
+      <c r="B19" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+      <c r="A20" s="9"/>
+      <c r="B20" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+      <c r="A21" s="9"/>
+      <c r="B21" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="I21" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="H17" s="14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J21" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="20"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="1" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="6"/>
       <c r="B24" s="6" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C24" s="7">
         <v>46124</v>
       </c>
+      <c r="D24" s="9"/>
       <c r="E24" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+      <c r="A25" s="9"/>
       <c r="B25" s="6" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="C25" s="7">
         <v>46128</v>
       </c>
+      <c r="D25" s="9"/>
       <c r="E25" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+      <c r="A26" s="9"/>
       <c r="B26" s="6" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C26" s="7">
         <v>46128</v>
       </c>
+      <c r="D26" s="9"/>
       <c r="E26" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+      <c r="A27" s="9"/>
       <c r="B27" s="6" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C27" s="7">
         <v>46133</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+      <c r="A28" s="9"/>
       <c r="B28" s="6" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C28" s="7">
         <v>46140</v>
       </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Market Makers Project Timeline.xlsx
+++ b/Market Makers Project Timeline.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edwar\OneDrive\Documents\Coding\ECE 554\ECE554_Capstone\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC691A93-EEFF-4190-8BF4-4796FE6E3D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="89">
   <si>
     <t>Project Part</t>
   </si>
@@ -73,9 +79,6 @@
   </si>
   <si>
     <t>Created hps_tcp_reciever.py and verified packet communcation between laptop and FPGA. Also created tcp_packet_reciever.v but unable to program the board succesfully.</t>
-  </si>
-  <si>
-    <t>Fixed issues connecting HPS and FPGA logic. Ethernet Input complete. Ethernet Output complete. Need to merge with ITCH translator.</t>
   </si>
   <si>
     <t>Parser</t>
@@ -278,23 +281,49 @@
     <t>Demo team (software showing all stocks &amp; info)</t>
   </si>
   <si>
-    <t xml:space="preserve">Execution tracker in python should have most information on inventory, profits, and trades ready, just needs to make graphs and look pretty. </t>
-  </si>
-  <si>
     <t>Final Improvements, bug fixes, and internal demo</t>
   </si>
   <si>
     <t>Poster &amp; Report Work</t>
+  </si>
+  <si>
+    <t>Fixed issues connecting HPS and FPGA logic. Ethernet Input complete. Ethernet Output complete. Ethenet Connected to both parser and translator</t>
+  </si>
+  <si>
+    <r>
+      <t>Execution tracker in python should have most information on inventory, profits, and trades ready, just needs to make graphs and look pretty.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Facing issues when connecting Parser and Orderbook.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Hope to fix by the end of 4/16.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> Facing issues when connecting Parser and Orderbook.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +362,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -343,17 +385,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00ff00"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF66ff33"/>
+        <fgColor rgb="FF66FF33"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFffff00"/>
+        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -374,16 +416,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -391,95 +433,84 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="4" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -490,10 +521,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -531,71 +562,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -623,7 +654,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -646,11 +677,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -659,13 +690,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -675,7 +706,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -684,7 +715,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -693,7 +724,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -701,10 +732,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -769,26 +800,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="23" width="26.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="24" width="38.14785714285715" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="25" width="17.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="23" width="17.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="23" width="96.14785714285713" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="26" width="31.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="26" width="29.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="26" width="29.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="23" width="22.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="23" width="13.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -818,7 +849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="44.25">
+    <row r="2" spans="1:10" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -831,16 +862,11 @@
       <c r="D2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="83.25">
+    </row>
+    <row r="3" spans="1:10" ht="83.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6" t="s">
         <v>14</v>
@@ -848,529 +874,403 @@
       <c r="C3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="D3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="39">
+      <c r="H3" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6"/>
       <c r="B4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="31.5">
+    </row>
+    <row r="5" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="G5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    </row>
+    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="10" t="s">
+      <c r="H6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="94.5">
+    </row>
+    <row r="7" spans="1:10" ht="94.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="14" t="s">
+      <c r="G7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="H7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="H7" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="47.25">
+    </row>
+    <row r="8" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="14" t="s">
+      <c r="G8" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="H8" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="27.75">
+    </row>
+    <row r="9" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="14"/>
+      <c r="G9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="31.5">
+    </row>
+    <row r="10" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="14" t="s">
+      <c r="H10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+    </row>
+    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="75">
+    </row>
+    <row r="12" spans="1:10" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="14" t="s">
+      <c r="F12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="H12" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="15" t="s">
+      <c r="G13" s="14"/>
+      <c r="H13" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="39">
+    </row>
+    <row r="14" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="15" t="s">
+    </row>
+    <row r="16" spans="1:10" s="10" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="57.75" customFormat="1" s="16">
-      <c r="A16" s="11"/>
-      <c r="B16" s="14" t="s">
+      <c r="C16" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="10" t="s">
+    </row>
+    <row r="17" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="9"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="31.5">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="10" t="s">
+      <c r="H18" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H18" s="11" t="s">
+    </row>
+    <row r="19" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="9"/>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="9" t="s">
+    </row>
+    <row r="20" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="9"/>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="9" t="s">
+    </row>
+    <row r="21" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="9"/>
-      <c r="B21" s="19" t="s">
+      <c r="C21" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="9" t="s">
+      <c r="E21" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="H21" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11" t="s">
+      <c r="I21" t="s">
         <v>75</v>
       </c>
-      <c r="I21" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="J21" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    </row>
+    <row r="22" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    </row>
+    <row r="23" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="11"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C24" s="7">
         <v>46124</v>
       </c>
-      <c r="D24" s="9"/>
       <c r="E24" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="9"/>
-      <c r="B25" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="C25" s="7">
         <v>46128</v>
       </c>
-      <c r="D25" s="9"/>
       <c r="E25" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="9"/>
-      <c r="B26" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="C26" s="7">
         <v>46128</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="9"/>
+      <c r="E26" s="21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C27" s="7">
         <v>46133</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="9"/>
+    </row>
+    <row r="28" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C28" s="7">
         <v>46140</v>
       </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>